--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.82870229289854</v>
+        <v>5.659664122596013</v>
       </c>
       <c r="D2" t="n">
-        <v>35.7128610153585</v>
+        <v>5.803339914995756</v>
       </c>
       <c r="E2" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F2" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.46157403542703</v>
+        <v>2.187505780756893</v>
       </c>
       <c r="D3" t="n">
-        <v>12.95389964091212</v>
+        <v>2.105008691648219</v>
       </c>
       <c r="E3" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F3" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.20701074278813</v>
+        <v>6.371139245703071</v>
       </c>
       <c r="D4" t="n">
-        <v>40.03568600787977</v>
+        <v>6.505798976280462</v>
       </c>
       <c r="E4" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F4" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.46535166595095</v>
+        <v>4.78811964571703</v>
       </c>
       <c r="D5" t="n">
-        <v>28.73366698940288</v>
+        <v>4.669220885777968</v>
       </c>
       <c r="E5" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F5" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.37227543812693</v>
+        <v>3.147994758695627</v>
       </c>
       <c r="D6" t="n">
-        <v>18.62892536591039</v>
+        <v>3.027200371960438</v>
       </c>
       <c r="E6" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F6" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.83884731890642</v>
+        <v>5.661312689322293</v>
       </c>
       <c r="D7" t="n">
-        <v>53.46002820586831</v>
+        <v>8.687254583453601</v>
       </c>
       <c r="E7" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F7" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.38124222469819</v>
+        <v>3.474451861513455</v>
       </c>
       <c r="D8" t="n">
-        <v>20.46134192045225</v>
+        <v>3.32496806207349</v>
       </c>
       <c r="E8" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F8" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.03286076408334</v>
+        <v>4.717839874163543</v>
       </c>
       <c r="D9" t="n">
-        <v>29.59349296226198</v>
+        <v>4.808942606367571</v>
       </c>
       <c r="E9" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F9" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75039265425651</v>
+        <v>4.671938806316684</v>
       </c>
       <c r="D10" t="n">
-        <v>43.80338935211104</v>
+        <v>7.118050769718044</v>
       </c>
       <c r="E10" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F10" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.95481670146271</v>
+        <v>5.03015771398769</v>
       </c>
       <c r="D11" t="n">
-        <v>24.67108523069195</v>
+        <v>4.009051349987441</v>
       </c>
       <c r="E11" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F11" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.64376710276925</v>
+        <v>4.654612154200004</v>
       </c>
       <c r="D12" t="n">
-        <v>26.82652505376099</v>
+        <v>4.359310321236161</v>
       </c>
       <c r="E12" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F12" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.61508166491502</v>
+        <v>3.837450770548692</v>
       </c>
       <c r="D13" t="n">
-        <v>18.04161157012775</v>
+        <v>2.931761880145759</v>
       </c>
       <c r="E13" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F13" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.14717080313613</v>
+        <v>5.711415255509621</v>
       </c>
       <c r="D14" t="n">
-        <v>8.603233174989516</v>
+        <v>1.398025390935796</v>
       </c>
       <c r="E14" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F14" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.2309302741204</v>
+        <v>5.400026169544565</v>
       </c>
       <c r="D15" t="n">
-        <v>2.133468089845073</v>
+        <v>0.3466885645998243</v>
       </c>
       <c r="E15" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F15" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.46806987371795</v>
+        <v>5.926061354479168</v>
       </c>
       <c r="D16" t="n">
-        <v>20.56146844764184</v>
+        <v>3.341238622741799</v>
       </c>
       <c r="E16" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F16" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.73327140657203</v>
+        <v>5.806656603567955</v>
       </c>
       <c r="D17" t="n">
-        <v>49.47749279398294</v>
+        <v>8.040092579022229</v>
       </c>
       <c r="E17" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F17" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>28.82933423392755</v>
+        <v>4.684766813013228</v>
       </c>
       <c r="D18" t="n">
-        <v>63.19702646720324</v>
+        <v>10.26951680092053</v>
       </c>
       <c r="E18" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F18" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>21.51618086232323</v>
+        <v>3.496379390127525</v>
       </c>
       <c r="D19" t="n">
-        <v>31.69739163163315</v>
+        <v>5.150826140140387</v>
       </c>
       <c r="E19" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F19" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>20.41717851375748</v>
+        <v>3.31779150848559</v>
       </c>
       <c r="D20" t="n">
-        <v>30.36453038682422</v>
+        <v>4.934236187858936</v>
       </c>
       <c r="E20" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F20" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>26.97315887241904</v>
+        <v>4.383138316768094</v>
       </c>
       <c r="D21" t="n">
-        <v>55.81072522046875</v>
+        <v>9.069242848326173</v>
       </c>
       <c r="E21" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F21" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23.54796918736984</v>
+        <v>3.826544992947599</v>
       </c>
       <c r="D22" t="n">
-        <v>6.474870994090166</v>
+        <v>1.052166536539652</v>
       </c>
       <c r="E22" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F22" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>28.23943153459173</v>
+        <v>4.588907624371157</v>
       </c>
       <c r="D23" t="n">
-        <v>48.64656553547242</v>
+        <v>7.905066899514268</v>
       </c>
       <c r="E23" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F23" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>29.50602177180773</v>
+        <v>4.794728537918757</v>
       </c>
       <c r="D24" t="n">
-        <v>55.58269334796097</v>
+        <v>9.032187669043658</v>
       </c>
       <c r="E24" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F24" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>22.09975898159572</v>
+        <v>3.591210834509305</v>
       </c>
       <c r="D25" t="n">
-        <v>49.91894486050861</v>
+        <v>8.111828539832649</v>
       </c>
       <c r="E25" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F25" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>7.068537111869961</v>
+        <v>1.148637280678869</v>
       </c>
       <c r="D26" t="n">
-        <v>24.07333998436163</v>
+        <v>3.911917747458765</v>
       </c>
       <c r="E26" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F26" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>53.78797485067992</v>
+        <v>8.740545913235486</v>
       </c>
       <c r="D27" t="n">
-        <v>38.56775086052355</v>
+        <v>6.267259514835078</v>
       </c>
       <c r="E27" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F27" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>26.56557279088724</v>
+        <v>4.316905578519177</v>
       </c>
       <c r="D28" t="n">
-        <v>56.26642102992911</v>
+        <v>9.143293417363481</v>
       </c>
       <c r="E28" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F28" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>35.24295609026611</v>
+        <v>5.726980364668243</v>
       </c>
       <c r="D29" t="n">
-        <v>65.19806870240535</v>
+        <v>10.59468616414087</v>
       </c>
       <c r="E29" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F29" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>27.11773599788215</v>
+        <v>4.406632099655849</v>
       </c>
       <c r="D30" t="n">
-        <v>54.11075139426873</v>
+        <v>8.79299710156867</v>
       </c>
       <c r="E30" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F30" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>47.98033828538544</v>
+        <v>7.796804971375135</v>
       </c>
       <c r="D31" t="n">
-        <v>77.95330837352448</v>
+        <v>12.66741261069773</v>
       </c>
       <c r="E31" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F31" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>26.07554873997476</v>
+        <v>4.237276670245899</v>
       </c>
       <c r="D32" t="n">
-        <v>49.57004073663287</v>
+        <v>8.055131619702841</v>
       </c>
       <c r="E32" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F32" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>55.55627386869921</v>
+        <v>9.027894503663621</v>
       </c>
       <c r="D33" t="n">
-        <v>44.89906435873682</v>
+        <v>7.296097958294733</v>
       </c>
       <c r="E33" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F33" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>38.41750899991182</v>
+        <v>6.242845212485671</v>
       </c>
       <c r="D34" t="n">
-        <v>63.38448133353063</v>
+        <v>10.29997821669873</v>
       </c>
       <c r="E34" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F34" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>35.4418797524585</v>
+        <v>5.759305459774506</v>
       </c>
       <c r="D35" t="n">
-        <v>49.48123523923885</v>
+        <v>8.040700726376313</v>
       </c>
       <c r="E35" t="n">
-        <v>9.794023823261984</v>
+        <v>1.591528871280073</v>
       </c>
       <c r="F35" t="n">
-        <v>18.5696532518164</v>
+        <v>3.017568653420165</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
